--- a/data.mn/public/datasets/mongolbank-mortgage-loans.xlsx
+++ b/data.mn/public/datasets/mongolbank-mortgage-loans.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,8 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -436,7 +439,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1032.16</v>
+        <v>1032.157</v>
       </c>
     </row>
     <row r="3">
@@ -446,7 +449,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1273</v>
+        <v>1273.004</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +459,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1461.75</v>
+        <v>1461.753</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +469,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1611.38</v>
+        <v>1611.384</v>
       </c>
     </row>
     <row r="6">
@@ -476,7 +479,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1750.78</v>
+        <v>1750.782</v>
       </c>
     </row>
     <row r="7">
@@ -486,7 +489,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1834.04</v>
+        <v>1834.043</v>
       </c>
     </row>
     <row r="8">
@@ -496,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1938.95</v>
+        <v>1938.945</v>
       </c>
     </row>
     <row r="9">
@@ -506,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2021.42</v>
+        <v>2021.425</v>
       </c>
     </row>
     <row r="10">
@@ -516,7 +519,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2121.8</v>
+        <v>2121.803</v>
       </c>
     </row>
     <row r="11">
@@ -526,7 +529,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2193.37</v>
+        <v>2193.369</v>
       </c>
     </row>
     <row r="12">
@@ -536,7 +539,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2280.5</v>
+        <v>2280.503</v>
       </c>
     </row>
     <row r="13">
@@ -556,7 +559,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2440.01</v>
+        <v>2440.007</v>
       </c>
     </row>
     <row r="15">
@@ -566,7 +569,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2492.11</v>
+        <v>2492.105</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +579,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2553.83</v>
+        <v>2553.827</v>
       </c>
     </row>
     <row r="17">
@@ -586,7 +589,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2619.16</v>
+        <v>2619.161</v>
       </c>
     </row>
     <row r="18">
@@ -596,7 +599,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2703.79</v>
+        <v>2703.793</v>
       </c>
     </row>
     <row r="19">
@@ -606,7 +609,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2762.73</v>
+        <v>2762.727</v>
       </c>
     </row>
     <row r="20">
@@ -616,7 +619,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2844.71</v>
+        <v>2844.706</v>
       </c>
     </row>
     <row r="21">
@@ -626,7 +629,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2898.73</v>
+        <v>2898.731</v>
       </c>
     </row>
     <row r="22">
@@ -636,7 +639,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2949.12</v>
+        <v>2949.117</v>
       </c>
     </row>
     <row r="23">
@@ -646,7 +649,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3015.54</v>
+        <v>3015.535</v>
       </c>
     </row>
     <row r="24">
@@ -656,7 +659,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3082.55</v>
+        <v>3082.552</v>
       </c>
     </row>
     <row r="25">
@@ -666,7 +669,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3128.18</v>
+        <v>3128.182</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +679,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3192.03</v>
+        <v>3192.029</v>
       </c>
     </row>
     <row r="27">
@@ -686,7 +689,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3230.51</v>
+        <v>3230.508</v>
       </c>
     </row>
     <row r="28">
@@ -696,7 +699,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3267.18</v>
+        <v>3267.175</v>
       </c>
     </row>
     <row r="29">
@@ -706,7 +709,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3319.71</v>
+        <v>3319.712</v>
       </c>
     </row>
     <row r="30">
@@ -736,7 +739,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3432.96</v>
+        <v>3432.958</v>
       </c>
     </row>
     <row r="33">
@@ -756,7 +759,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3459.6</v>
+        <v>3459.597</v>
       </c>
     </row>
     <row r="35">
@@ -766,7 +769,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3565.32</v>
+        <v>3565.321</v>
       </c>
     </row>
     <row r="36">
@@ -776,7 +779,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3632.98</v>
+        <v>3632.982</v>
       </c>
     </row>
     <row r="37">
@@ -786,7 +789,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3697.06</v>
+        <v>3697.057</v>
       </c>
     </row>
     <row r="38">
@@ -796,7 +799,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3792.28</v>
+        <v>3792.276</v>
       </c>
     </row>
     <row r="39">
@@ -806,7 +809,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3849.22</v>
+        <v>3849.221</v>
       </c>
     </row>
     <row r="40">
@@ -816,7 +819,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3886.36</v>
+        <v>3886.363</v>
       </c>
     </row>
     <row r="41">
@@ -826,7 +829,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3943.04</v>
+        <v>3943.037</v>
       </c>
     </row>
     <row r="42">
@@ -836,7 +839,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3950.19</v>
+        <v>3950.187</v>
       </c>
     </row>
     <row r="43">
@@ -846,7 +849,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3979.62</v>
+        <v>3979.616</v>
       </c>
     </row>
     <row r="44">
@@ -856,7 +859,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4018.3</v>
+        <v>4018.298</v>
       </c>
     </row>
     <row r="45">
@@ -866,7 +869,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4034.89</v>
+        <v>4034.887</v>
       </c>
     </row>
     <row r="46">
@@ -876,7 +879,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4062.8</v>
+        <v>4062.801</v>
       </c>
     </row>
     <row r="47">
@@ -886,7 +889,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4091.15</v>
+        <v>4091.152</v>
       </c>
     </row>
     <row r="48">
@@ -896,7 +899,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4112.25</v>
+        <v>4112.247</v>
       </c>
     </row>
     <row r="49">
@@ -906,7 +909,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4143.15</v>
+        <v>4143.155</v>
       </c>
     </row>
     <row r="50">
@@ -926,7 +929,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4186.06</v>
+        <v>4186.061</v>
       </c>
     </row>
     <row r="52">
@@ -946,7 +949,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4206.82</v>
+        <v>4206.817</v>
       </c>
     </row>
     <row r="54">
@@ -956,7 +959,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4217.73</v>
+        <v>4217.735</v>
       </c>
     </row>
     <row r="55">
@@ -966,7 +969,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4231.84</v>
+        <v>4231.843</v>
       </c>
     </row>
     <row r="56">
@@ -976,7 +979,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4253.22</v>
+        <v>4253.222</v>
       </c>
     </row>
     <row r="57">
@@ -986,7 +989,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4247.2</v>
+        <v>4247.201</v>
       </c>
     </row>
     <row r="58">
@@ -996,7 +999,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4243.87</v>
+        <v>4243.873</v>
       </c>
     </row>
     <row r="59">
@@ -1006,7 +1009,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4255.13</v>
+        <v>4255.135</v>
       </c>
     </row>
     <row r="60">
@@ -1016,7 +1019,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4261.46</v>
+        <v>4261.455</v>
       </c>
     </row>
     <row r="61">
@@ -1026,7 +1029,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4293.1</v>
+        <v>4293.097</v>
       </c>
     </row>
     <row r="62">
@@ -1046,7 +1049,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4331.8</v>
+        <v>4331.802</v>
       </c>
     </row>
     <row r="64">
@@ -1056,7 +1059,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4341.01</v>
+        <v>4341.011</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1069,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4350.3</v>
+        <v>4350.297</v>
       </c>
     </row>
     <row r="66">
@@ -1076,7 +1079,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4357.51</v>
+        <v>4357.511</v>
       </c>
     </row>
     <row r="67">
@@ -1086,7 +1089,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4385.38</v>
+        <v>4385.378</v>
       </c>
     </row>
     <row r="68">
@@ -1116,7 +1119,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4413.35</v>
+        <v>4413.353</v>
       </c>
     </row>
     <row r="71">
@@ -1136,7 +1139,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4437.51</v>
+        <v>4437.506</v>
       </c>
     </row>
     <row r="73">
@@ -1146,7 +1149,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4473.76</v>
+        <v>4473.755</v>
       </c>
     </row>
     <row r="74">
@@ -1156,7 +1159,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4488.23</v>
+        <v>4488.231</v>
       </c>
     </row>
     <row r="75">
@@ -1166,7 +1169,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4501.08</v>
+        <v>4501.079</v>
       </c>
     </row>
     <row r="76">
@@ -1176,7 +1179,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4518.29</v>
+        <v>4518.295</v>
       </c>
     </row>
     <row r="77">
@@ -1186,7 +1189,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4532.03</v>
+        <v>4532.031</v>
       </c>
     </row>
     <row r="78">
@@ -1196,7 +1199,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4552.89</v>
+        <v>4552.886</v>
       </c>
     </row>
     <row r="79">
@@ -1206,7 +1209,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4574.26</v>
+        <v>4574.261</v>
       </c>
     </row>
     <row r="80">
@@ -1216,7 +1219,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4628.96</v>
+        <v>4628.958</v>
       </c>
     </row>
     <row r="81">
@@ -1226,7 +1229,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4629.15</v>
+        <v>4629.149</v>
       </c>
     </row>
     <row r="82">
@@ -1236,7 +1239,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4638.58</v>
+        <v>4638.578</v>
       </c>
     </row>
     <row r="83">
@@ -1246,7 +1249,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4640.31</v>
+        <v>4640.306</v>
       </c>
     </row>
     <row r="84">
@@ -1256,7 +1259,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4654.79</v>
+        <v>4654.785</v>
       </c>
     </row>
     <row r="85">
@@ -1266,7 +1269,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4682.5</v>
+        <v>4682.501</v>
       </c>
     </row>
     <row r="86">
@@ -1276,7 +1279,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4730.87</v>
+        <v>4730.866</v>
       </c>
     </row>
     <row r="87">
@@ -1286,7 +1289,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4763.95</v>
+        <v>4763.948</v>
       </c>
     </row>
     <row r="88">
@@ -1296,7 +1299,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4807.69</v>
+        <v>4807.692</v>
       </c>
     </row>
     <row r="89">
@@ -1306,7 +1309,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4835.56</v>
+        <v>4835.558</v>
       </c>
     </row>
     <row r="90">
@@ -1316,7 +1319,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4867.07</v>
+        <v>4867.074</v>
       </c>
     </row>
     <row r="91">
@@ -1326,7 +1329,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4870</v>
+        <v>4870.003</v>
       </c>
     </row>
     <row r="92">
@@ -1336,7 +1339,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4919.17</v>
+        <v>4919.174</v>
       </c>
     </row>
     <row r="93">
@@ -1346,7 +1349,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4933.14</v>
+        <v>4933.139</v>
       </c>
     </row>
     <row r="94">
@@ -1356,7 +1359,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4947.16</v>
+        <v>4947.159</v>
       </c>
     </row>
     <row r="95">
@@ -1366,7 +1369,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5020.33</v>
+        <v>5020.331</v>
       </c>
     </row>
     <row r="96">
@@ -1376,7 +1379,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5050.89</v>
+        <v>5050.892</v>
       </c>
     </row>
     <row r="97">
@@ -1386,7 +1389,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5093.27</v>
+        <v>5093.268</v>
       </c>
     </row>
     <row r="98">
@@ -1396,7 +1399,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5189.46</v>
+        <v>5189.456</v>
       </c>
     </row>
     <row r="99">
@@ -1406,7 +1409,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5253.05</v>
+        <v>5253.048</v>
       </c>
     </row>
     <row r="100">
@@ -1416,7 +1419,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5372.05</v>
+        <v>5372.049</v>
       </c>
     </row>
     <row r="101">
@@ -1426,7 +1429,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5452.46</v>
+        <v>5452.461</v>
       </c>
     </row>
     <row r="102">
@@ -1436,7 +1439,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5518.36</v>
+        <v>5518.364</v>
       </c>
     </row>
     <row r="103">
@@ -1446,7 +1449,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5578.41</v>
+        <v>5578.407</v>
       </c>
     </row>
     <row r="104">
@@ -1456,7 +1459,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5654.48</v>
+        <v>5654.482</v>
       </c>
     </row>
     <row r="105">
@@ -1466,7 +1469,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5700.33</v>
+        <v>5700.334</v>
       </c>
     </row>
     <row r="106">
@@ -1476,7 +1479,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5729.43</v>
+        <v>5729.425</v>
       </c>
     </row>
     <row r="107">
@@ -1486,7 +1489,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5800.31</v>
+        <v>5800.311</v>
       </c>
     </row>
     <row r="108">
@@ -1496,7 +1499,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5860.4</v>
+        <v>5860.403</v>
       </c>
     </row>
     <row r="109">
@@ -1506,7 +1509,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5928.95</v>
+        <v>5928.954</v>
       </c>
     </row>
     <row r="110">
@@ -1536,7 +1539,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>6112.47</v>
+        <v>6112.468</v>
       </c>
     </row>
     <row r="113">
@@ -1546,7 +1549,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>6190.48</v>
+        <v>6190.477</v>
       </c>
     </row>
     <row r="114">
@@ -1556,7 +1559,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>6281.36</v>
+        <v>6281.364</v>
       </c>
     </row>
     <row r="115">
@@ -1566,7 +1569,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>6377.31</v>
+        <v>6377.313</v>
       </c>
     </row>
     <row r="116">
@@ -1586,7 +1589,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>6505.67</v>
+        <v>6505.669</v>
       </c>
     </row>
     <row r="118">
@@ -1596,7 +1599,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>6575.69</v>
+        <v>6575.685</v>
       </c>
     </row>
     <row r="119">
@@ -1606,7 +1609,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>6663.41</v>
+        <v>6663.409</v>
       </c>
     </row>
     <row r="120">
@@ -1616,7 +1619,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>6741.68</v>
+        <v>6741.678</v>
       </c>
     </row>
     <row r="121">
@@ -1636,7 +1639,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>6905.9</v>
+        <v>6905.903</v>
       </c>
     </row>
     <row r="123">
@@ -1646,7 +1649,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>6928.03</v>
+        <v>6928.027</v>
       </c>
     </row>
     <row r="124">
@@ -1656,7 +1659,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>6994.52</v>
+        <v>6994.522</v>
       </c>
     </row>
     <row r="125">
@@ -1666,7 +1669,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>7120.65</v>
+        <v>7120.651</v>
       </c>
     </row>
     <row r="126">
@@ -1676,7 +1679,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>7272.33</v>
+        <v>7272.327</v>
       </c>
     </row>
     <row r="127">
@@ -1686,7 +1689,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>7435.87</v>
+        <v>7435.866</v>
       </c>
     </row>
     <row r="128">
@@ -1696,7 +1699,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>7644.26</v>
+        <v>7644.256</v>
       </c>
     </row>
     <row r="129">
@@ -1706,7 +1709,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>7724.82</v>
+        <v>7724.824</v>
       </c>
     </row>
     <row r="130">
@@ -1716,7 +1719,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>7813.43</v>
+        <v>7813.429</v>
       </c>
     </row>
     <row r="131">
@@ -1726,7 +1729,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>7917.77</v>
+        <v>7917.766</v>
       </c>
     </row>
     <row r="132">
@@ -1736,7 +1739,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>8051.71</v>
+        <v>8051.706</v>
       </c>
     </row>
     <row r="133">
@@ -1746,7 +1749,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>8280.17</v>
+        <v>8280.174999999999</v>
       </c>
     </row>
     <row r="134">
@@ -1756,7 +1759,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>8559.280000000001</v>
+        <v>8559.279</v>
       </c>
     </row>
     <row r="135">
@@ -1766,7 +1769,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>8722.139999999999</v>
+        <v>8722.137000000001</v>
       </c>
     </row>
     <row r="136">
@@ -1776,7 +1779,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>8832.559999999999</v>
+        <v>8832.564</v>
       </c>
     </row>
     <row r="137">
@@ -1786,7 +1789,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>8962.450000000001</v>
+        <v>8962.454</v>
       </c>
     </row>
     <row r="138">
@@ -1796,7 +1799,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>9096.280000000001</v>
+        <v>9096.277</v>
       </c>
     </row>
     <row r="139">
@@ -1806,7 +1809,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>9237.92</v>
+        <v>9237.922</v>
       </c>
     </row>
     <row r="140">
@@ -1826,7 +1829,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>9529.209999999999</v>
+        <v>9529.213</v>
       </c>
     </row>
     <row r="142">
@@ -1836,7 +1839,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>9671.440000000001</v>
+        <v>9671.437</v>
       </c>
     </row>
     <row r="143">
@@ -1846,7 +1849,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>9778.26</v>
+        <v>9778.254999999999</v>
       </c>
     </row>
     <row r="144">
@@ -1856,7 +1859,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>9976.75</v>
+        <v>9976.751</v>
       </c>
     </row>
     <row r="145">
@@ -1866,7 +1869,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>10178.44</v>
+        <v>10178.436</v>
       </c>
     </row>
     <row r="146">
@@ -1876,7 +1879,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>10377.29</v>
+        <v>10377.287</v>
       </c>
     </row>
     <row r="147">
@@ -1896,7 +1899,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>10582.56</v>
+        <v>10582.559</v>
       </c>
     </row>
     <row r="149">
@@ -1906,7 +1909,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>10798.84</v>
+        <v>10798.844</v>
       </c>
     </row>
     <row r="150">
@@ -1916,7 +1919,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>11044.12</v>
+        <v>11044.122</v>
       </c>
     </row>
     <row r="151">
@@ -1926,7 +1929,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>11227.76</v>
+        <v>11227.764</v>
       </c>
     </row>
     <row r="152">
@@ -1936,7 +1939,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>11477.8</v>
+        <v>11477.797</v>
       </c>
     </row>
     <row r="153">
@@ -1946,7 +1949,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>11568.81</v>
+        <v>11568.806</v>
       </c>
     </row>
     <row r="154">
@@ -1956,1563 +1959,57 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>11672.16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B154"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>огноо</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ипотекийн_зээл_тэрбум_төгрөг</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2013-06-01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1032.16</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2013-07-01</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2013-08-01</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1461.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2013-09-01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1611.38</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2013-10-01</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1750.78</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2013-11-01</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1834.04</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2013-12-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1938.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2021.42</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2014-02-01</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2121.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2014-03-01</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2193.37</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2014-04-01</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2280.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2014-05-01</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2365.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2014-06-01</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2440.01</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2492.11</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2014-08-01</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2553.83</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2619.16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2014-10-01</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2703.79</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2014-11-01</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2762.73</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2014-12-01</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2844.71</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2898.73</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2015-02-01</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2949.12</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2015-03-01</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3015.54</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3082.55</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2015-05-01</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>3128.18</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2015-06-01</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>3192.03</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2015-07-01</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3230.51</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2015-08-01</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3267.18</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2015-09-01</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3319.71</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2015-10-01</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>3370.51</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2015-11-01</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3412.93</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2015-12-01</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3432.96</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3434.85</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2016-02-01</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3459.6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2016-03-01</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3565.32</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2016-04-01</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3632.98</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2016-05-01</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>3697.06</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2016-06-01</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3792.28</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2016-07-01</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3849.22</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2016-08-01</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3886.36</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>3943.04</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2016-10-01</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3950.19</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2016-11-01</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>3979.62</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2016-12-01</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>4018.3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>4034.89</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2017-02-01</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>4062.8</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2017-03-01</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4091.15</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2017-04-01</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4112.25</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2017-05-01</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>4143.15</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2017-06-01</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>4177.18</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2017-07-01</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>4186.06</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2017-08-01</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>4196.17</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2017-09-01</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>4206.82</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2017-10-01</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>4217.73</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2017-11-01</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>4231.84</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2017-12-01</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>4253.22</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>4247.2</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2018-02-01</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4243.87</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2018-03-01</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>4255.13</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2018-04-01</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>4261.46</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2018-05-01</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>4293.1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2018-06-01</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>4328.51</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>4331.8</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2018-08-01</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>4341.01</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>4350.3</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2018-10-01</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>4357.51</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>4385.38</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2018-12-01</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>4430.22</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>4424.84</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2019-02-01</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>4413.35</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2019-03-01</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>4413.73</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2019-04-01</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>4437.51</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2019-05-01</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>4473.76</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>4488.23</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2019-07-01</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>4501.08</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2019-08-01</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>4518.29</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2019-09-01</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>4532.03</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2019-10-01</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>4552.89</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2019-11-01</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>4574.26</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2019-12-01</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>4628.96</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>4629.15</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2020-02-01</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>4638.58</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2020-03-01</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>4640.31</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2020-04-01</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>4654.79</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2020-05-01</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>4682.5</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2020-06-01</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>4730.87</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>4763.95</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2020-08-01</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>4807.69</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>4835.56</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>4867.07</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2020-11-01</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>4870</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2020-12-01</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>4919.17</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>4933.14</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2021-02-01</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>4947.16</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2021-03-01</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>5020.33</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2021-04-01</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>5050.89</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2021-05-01</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>5093.27</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>5189.46</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>5253.05</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2021-08-01</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>5372.05</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>5452.46</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2021-10-01</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>5518.36</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>5578.41</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2021-12-01</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>5654.48</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>5700.33</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>5729.43</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2022-03-01</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>5800.31</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>5860.4</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>5928.95</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2022-06-01</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>5993.58</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>6043.82</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>6112.47</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>6190.48</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>6281.36</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>6377.31</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>6487.8</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>6505.67</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>6575.69</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>6663.41</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2023-04-01</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>6741.68</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2023-05-01</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>6823.1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>6905.9</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>6928.03</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>6994.52</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>7120.65</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2023-10-01</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>7272.33</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2023-11-01</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>7435.87</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2023-12-01</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>7644.26</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>7724.82</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2024-02-01</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>7813.43</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>7917.77</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>8051.71</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>8280.17</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>8559.280000000001</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>8722.139999999999</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>8832.559999999999</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>8962.450000000001</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>9096.280000000001</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>9237.92</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>9433.34</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>9529.209999999999</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>9671.440000000001</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>9778.26</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>9976.75</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>10178.44</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>10377.29</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>10465.64</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>10582.56</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>10798.84</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>11044.12</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>11227.76</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>11477.8</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>11568.81</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>11672.16</v>
+        <v>11672.164</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>11809.253</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>11964.812</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>12141.133</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>12324.917</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>12415.588</v>
       </c>
     </row>
   </sheetData>
